--- a/Tailieu/Nganhangdaimport/NHIP_T9.xlsx
+++ b/Tailieu/Nganhangdaimport/NHIP_T9.xlsx
@@ -50,7 +50,7 @@
     <t>Chọn</t>
   </si>
   <si>
-    <t>9/138</t>
+    <t>ACB109/01</t>
   </si>
   <si>
     <t>LUU VAN HAI chuyen tien.CT tu 1055943527 LUU VAN HAI toi 6000201008933 Cty TNHH Thuy San Cha Va Long Son tai AGRIBANK</t>
@@ -68,7 +68,7 @@
     <t>DLVH</t>
   </si>
   <si>
-    <t>9/137</t>
+    <t>ACB109/02</t>
   </si>
   <si>
     <t>HA VAN ANH chuyen tien.CT tu 0121001247300 HA VAN ANH toi 6000201008933 Cty TNHH Thuy San Cha Va Long Son tai AGRIBANK</t>
@@ -80,7 +80,7 @@
     <t>BCNTDVA</t>
   </si>
   <si>
-    <t>9/136</t>
+    <t>ACB109/03</t>
   </si>
   <si>
     <t>TRUONG DAC BINH CHUYEN KHOAN</t>
@@ -92,7 +92,7 @@
     <t>BCNTDDB</t>
   </si>
   <si>
-    <t>9/135</t>
+    <t>ACB109/04</t>
   </si>
   <si>
     <t>TRAN VAN BAN chuyen tien</t>
@@ -104,7 +104,7 @@
     <t>DTVB</t>
   </si>
   <si>
-    <t>9/134</t>
+    <t>ACB109/05</t>
   </si>
   <si>
     <t>BUI THI TUYEN chuyen tien.CT tu 9905376768 BUI THI TUYEN toi 6000201008933 Cty TNHH Thuy San Cha Va Long Son tai AGRIBANK</t>
@@ -116,7 +116,7 @@
     <t>TT_1</t>
   </si>
   <si>
-    <t>9/133</t>
+    <t>ACB109/06</t>
   </si>
   <si>
     <t>Le Van Bien chuyen tien</t>
@@ -128,7 +128,7 @@
     <t>DLVT</t>
   </si>
   <si>
-    <t>9/132</t>
+    <t>ACB109/07</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau THANH</t>
@@ -143,13 +143,13 @@
     <t>UBND-MS</t>
   </si>
   <si>
-    <t>9/131</t>
+    <t>ACB109/08</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca HUONG BIEN</t>
   </si>
   <si>
-    <t>9/130</t>
+    <t>ACB109/09</t>
   </si>
   <si>
     <t>NGUYEN DUC DUNG chuyen tien</t>
@@ -161,7 +161,7 @@
     <t>BCNTDDD</t>
   </si>
   <si>
-    <t>9/129</t>
+    <t>ACB109/10</t>
   </si>
   <si>
     <t>NGUYEN THI BINH chuyen tien</t>
@@ -173,61 +173,61 @@
     <t>DNTB</t>
   </si>
   <si>
-    <t>9/128</t>
+    <t>ACB109/11</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca HOANG</t>
   </si>
   <si>
-    <t>9/127</t>
+    <t>ACB109/12</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca BINH</t>
   </si>
   <si>
-    <t>9/126</t>
+    <t>ACB109/13</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien cua HOANG TIEN</t>
   </si>
   <si>
-    <t>9/125</t>
+    <t>ACB109/14</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien tom DUNG SY</t>
   </si>
   <si>
-    <t>9/124</t>
+    <t>ACB109/15</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ngheu HONG NGOC</t>
   </si>
   <si>
-    <t>9/123</t>
+    <t>ACB109/16</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien so HOANG PHAT</t>
   </si>
   <si>
-    <t>9/122</t>
+    <t>ACB109/17</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca tom TRUONG THANH</t>
   </si>
   <si>
-    <t>9/121</t>
+    <t>ACB109/18</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca NAM DIEN</t>
   </si>
   <si>
-    <t>9/120</t>
+    <t>ACB109/19</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien nuoc da thang 8</t>
   </si>
   <si>
-    <t>9/119</t>
+    <t>ACB109/20</t>
   </si>
   <si>
     <t>PHAM THI HUONG chuyen tien</t>
@@ -239,7 +239,7 @@
     <t>HE</t>
   </si>
   <si>
-    <t>9/118</t>
+    <t>ACB109/21</t>
   </si>
   <si>
     <t>VTU-02-064573, Vien Thong, 08/2026</t>
@@ -254,7 +254,7 @@
     <t>1042324*</t>
   </si>
   <si>
-    <t>9/117</t>
+    <t>ACB109/22</t>
   </si>
   <si>
     <t>VTU-01-233071, Vien Thong, 08/2026</t>
@@ -263,7 +263,7 @@
     <t>1042297*</t>
   </si>
   <si>
-    <t>9/116</t>
+    <t>ACB109/23</t>
   </si>
   <si>
     <t>VTU-02-064879, Vien Thong, 08/2026</t>
@@ -272,7 +272,7 @@
     <t>1042578*</t>
   </si>
   <si>
-    <t>9/115</t>
+    <t>ACB109/24</t>
   </si>
   <si>
     <t>VTU-01-233070, Vien Thong, 08/2026</t>
@@ -281,7 +281,7 @@
     <t>1042296*</t>
   </si>
   <si>
-    <t>9/114</t>
+    <t>ACB109/25</t>
   </si>
   <si>
     <t>VTU-01-231754, Vien Thong, 08/2026</t>
@@ -290,7 +290,7 @@
     <t>1041731*</t>
   </si>
   <si>
-    <t>9/113</t>
+    <t>ACB109/26</t>
   </si>
   <si>
     <t>PB15010137189, Dien, 09/26</t>
@@ -305,7 +305,7 @@
     <t>1937406*</t>
   </si>
   <si>
-    <t>9/112</t>
+    <t>ACB109/27</t>
   </si>
   <si>
     <t>VTU-02-064576, Vien Thong, 08/2026</t>
@@ -314,7 +314,7 @@
     <t>1042326*</t>
   </si>
   <si>
-    <t>9/111</t>
+    <t>ACB109/28</t>
   </si>
   <si>
     <t>6000LDS202600482</t>
@@ -323,7 +323,7 @@
     <t>1111</t>
   </si>
   <si>
-    <t>9/110</t>
+    <t>ACB109/29</t>
   </si>
   <si>
     <t>NGUYEN THI MAN chuyen tien.CT tu 0081001308557 NGUYEN THI MAN toi 6000201008933 Cty TNHH Thuy San Cha Va Long Son tai AGRIBANK</t>
@@ -335,13 +335,13 @@
     <t>DNTM</t>
   </si>
   <si>
-    <t>9/109</t>
+    <t>ACB109/30</t>
   </si>
   <si>
     <t>Phi DV SMS Banking T08/2026</t>
   </si>
   <si>
-    <t>9/108</t>
+    <t>ACB109/31</t>
   </si>
   <si>
     <t>Bang Lang Quan chuyen khoan nhanh qua Zalo</t>
@@ -353,22 +353,22 @@
     <t>3362</t>
   </si>
   <si>
-    <t>9/107</t>
-  </si>
-  <si>
-    <t>9/106</t>
+    <t>ACB109/32</t>
+  </si>
+  <si>
+    <t>ACB109/33</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ton lanh mau</t>
   </si>
   <si>
-    <t>9/105</t>
+    <t>ACB109/34</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca MINH CUONG</t>
   </si>
   <si>
-    <t>9/104</t>
+    <t>ACB109/35</t>
   </si>
   <si>
     <t>TT TIEN HAI SAN HD 1281+1268+1261+1255+1239+1219+1220+1227+1200+1180+1191</t>
@@ -380,19 +380,19 @@
     <t>5313</t>
   </si>
   <si>
-    <t>9/103</t>
+    <t>ACB109/36</t>
   </si>
   <si>
     <t>TT TIEN HAI SAN HD 1282+1242+1253+1262+1271+1181+1190+1189+1201+1216+1228 NGAY 5-9-2026</t>
   </si>
   <si>
-    <t>9/102</t>
+    <t>ACB109/37</t>
   </si>
   <si>
     <t>TT TIEN HAI SAN HD 1283+1272+1263+1254+1243+1182+1188+1202+1217+1229 NGAY 5-9-2026</t>
   </si>
   <si>
-    <t>9/101</t>
+    <t>ACB109/38</t>
   </si>
   <si>
     <t>Phuoc Nguyen TT tien hang HD 1195 den 1231 Cty Cha Va LS</t>
@@ -404,7 +404,7 @@
     <t>7853</t>
   </si>
   <si>
-    <t>9/100</t>
+    <t>ACB109/39</t>
   </si>
   <si>
     <t>LE PHU DO chuyen tien</t>
@@ -416,172 +416,172 @@
     <t>DLPD</t>
   </si>
   <si>
-    <t>9/99</t>
+    <t>ACB109/40</t>
   </si>
   <si>
     <t>TRAN VAN MUOI-RUT SEC AS7480063</t>
   </si>
   <si>
-    <t>9/98</t>
+    <t>ACB109/41</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son tien thue mat bang Q 3 va 4 nam 2026</t>
   </si>
   <si>
-    <t>9/97</t>
+    <t>ACB109/42</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hang THANH</t>
   </si>
   <si>
-    <t>9/96</t>
-  </si>
-  <si>
-    <t>9/95</t>
+    <t>ACB109/43</t>
+  </si>
+  <si>
+    <t>ACB109/44</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca Binh</t>
   </si>
   <si>
-    <t>9/94</t>
+    <t>ACB109/45</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca HAN</t>
   </si>
   <si>
-    <t>9/93</t>
-  </si>
-  <si>
-    <t>9/92</t>
+    <t>ACB109/46</t>
+  </si>
+  <si>
+    <t>ACB109/47</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau HOI</t>
   </si>
   <si>
-    <t>9/91</t>
+    <t>ACB109/48</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien tom DUNG SI</t>
   </si>
   <si>
-    <t>9/90</t>
+    <t>ACB109/49</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh tien so HOANG PHAT</t>
   </si>
   <si>
-    <t>9/89</t>
-  </si>
-  <si>
-    <t>9/88</t>
+    <t>ACB109/50</t>
+  </si>
+  <si>
+    <t>ACB109/51</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thang toan tien cua HOANG TIEN</t>
   </si>
   <si>
-    <t>9/87</t>
+    <t>ACB109/52</t>
   </si>
   <si>
     <t>C/C Transfer TO: #6000205272265 : CHI LUONG THANG 08/2026</t>
   </si>
   <si>
-    <t>9/86</t>
+    <t>ACB109/53</t>
   </si>
   <si>
     <t>C/C Transfer TO: #6000205717077 : CHI LUONG THANG 08/2026</t>
   </si>
   <si>
-    <t>9/85</t>
+    <t>ACB109/54</t>
   </si>
   <si>
     <t>C/C Transfer TO: #6000205877885 : CHI LUONG THANG 08/2026</t>
   </si>
   <si>
-    <t>9/84</t>
+    <t>ACB109/55</t>
   </si>
   <si>
     <t>C/C Transfer TO: #6000205877862 : CHI LUONG THANG 08/2026</t>
   </si>
   <si>
-    <t>9/83</t>
+    <t>ACB109/56</t>
   </si>
   <si>
     <t>C/C Transfer TO: #6000205870959 : CHI LUONG THANG 08/2026</t>
   </si>
   <si>
-    <t>9/82</t>
+    <t>ACB109/57</t>
   </si>
   <si>
     <t>C/C Transfer TO: #6000205639783 : CHI LUONG THANG 08/2026</t>
   </si>
   <si>
-    <t>9/81</t>
+    <t>ACB109/58</t>
   </si>
   <si>
     <t>C/C Transfer TO: #6000205663815 : CHI LUONG THANG 08/2026</t>
   </si>
   <si>
-    <t>9/80</t>
+    <t>ACB109/59</t>
   </si>
   <si>
     <t>C/C Transfer TO: #6000205717048 : CHI LUONG THANG 08/2026</t>
   </si>
   <si>
-    <t>9/79</t>
+    <t>ACB109/60</t>
   </si>
   <si>
     <t>C/C Transfer TO: #6000205717054 : CHI LUONG THANG 08/2026</t>
   </si>
   <si>
-    <t>9/78</t>
+    <t>ACB109/61</t>
   </si>
   <si>
     <t>C/C Transfer TO: #6000205660360 : CHI LUONG THANG 08/2026</t>
   </si>
   <si>
-    <t>9/77</t>
+    <t>ACB109/62</t>
   </si>
   <si>
     <t>C/C Transfer TO: #6000205877891 : CHI LUONG THANG 08/2026</t>
   </si>
   <si>
-    <t>9/76</t>
+    <t>ACB109/63</t>
   </si>
   <si>
     <t>C/C Transfer TO: #6000205487444 : CHI LUONG THANG 08/2026</t>
   </si>
   <si>
-    <t>9/75</t>
+    <t>ACB109/64</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien mua nhotv</t>
   </si>
   <si>
-    <t>9/74</t>
+    <t>ACB109/65</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau DUNG</t>
   </si>
   <si>
-    <t>9/73</t>
+    <t>ACB109/66</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau TUAN</t>
   </si>
   <si>
-    <t>9/72</t>
+    <t>ACB109/67</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau Co LANH</t>
   </si>
   <si>
-    <t>9/71</t>
+    <t>ACB109/68</t>
   </si>
   <si>
     <t>Phuoc nguyen TT tien hang HD tu 1247 den 1309 Cty Cha Va LS</t>
   </si>
   <si>
-    <t>9/70</t>
+    <t>ACB109/69</t>
   </si>
   <si>
     <t>NGUYEN HUU TIEN CHUYEN KHOAN</t>
@@ -593,10 +593,10 @@
     <t>DNHT</t>
   </si>
   <si>
-    <t>9/69</t>
-  </si>
-  <si>
-    <t>9/68</t>
+    <t>ACB109/70</t>
+  </si>
+  <si>
+    <t>ACB109/71</t>
   </si>
   <si>
     <t>Ca chim</t>
@@ -611,7 +611,7 @@
     <t>1349*</t>
   </si>
   <si>
-    <t>9/67</t>
+    <t>ACB109/72</t>
   </si>
   <si>
     <t>So long</t>
@@ -620,40 +620,40 @@
     <t>1352*</t>
   </si>
   <si>
-    <t>9/66</t>
+    <t>ACB109/73</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau LANH</t>
   </si>
   <si>
-    <t>9/65</t>
+    <t>ACB109/74</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan toen ca MINH CUONG</t>
   </si>
   <si>
-    <t>9/64</t>
-  </si>
-  <si>
-    <t>9/63</t>
+    <t>ACB109/75</t>
+  </si>
+  <si>
+    <t>ACB109/76</t>
   </si>
   <si>
     <t>TT TIEN HAI SAN HD 1344+1190+1292+1298+1306+1315+1326+1332 ngay 12-09-2026</t>
   </si>
   <si>
-    <t>9/62</t>
+    <t>ACB109/77</t>
   </si>
   <si>
     <t>TT TIEN HAI SAN HD 1353+1343+1290+1297+1308+1314+1325+1331 NGAY 13-09-2023</t>
   </si>
   <si>
-    <t>9/61</t>
+    <t>ACB109/78</t>
   </si>
   <si>
     <t>TT TIEN HAI SAN HD 1345+1291+1299+1307+1316+1327+1333 ngay 12-09-2026</t>
   </si>
   <si>
-    <t>9/60</t>
+    <t>ACB109/79</t>
   </si>
   <si>
     <t>5469532, Nuoc, 9/2026</t>
@@ -668,37 +668,37 @@
     <t>1579385*</t>
   </si>
   <si>
-    <t>9/59</t>
+    <t>ACB109/80</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca TRUONG THANH</t>
   </si>
   <si>
-    <t>9/58</t>
-  </si>
-  <si>
-    <t>9/57</t>
-  </si>
-  <si>
-    <t>9/56</t>
-  </si>
-  <si>
-    <t>9/55</t>
-  </si>
-  <si>
-    <t>9/54</t>
+    <t>ACB109/81</t>
+  </si>
+  <si>
+    <t>ACB109/82</t>
+  </si>
+  <si>
+    <t>ACB109/83</t>
+  </si>
+  <si>
+    <t>ACB109/84</t>
+  </si>
+  <si>
+    <t>ACB109/85</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thang toan tien ca HAN</t>
   </si>
   <si>
-    <t>9/53</t>
+    <t>ACB109/86</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca THE</t>
   </si>
   <si>
-    <t>9/52</t>
+    <t>ACB109/87</t>
   </si>
   <si>
     <t>Chi dung Zalopay chuyen tien</t>
@@ -710,22 +710,22 @@
     <t>BCNTD-CD</t>
   </si>
   <si>
-    <t>9/51</t>
-  </si>
-  <si>
-    <t>9/50</t>
+    <t>ACB109/88</t>
+  </si>
+  <si>
+    <t>ACB109/89</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien lap camera xe 72 C 02885</t>
   </si>
   <si>
-    <t>9/49</t>
+    <t>ACB109/90</t>
   </si>
   <si>
     <t>6000LDS202601410</t>
   </si>
   <si>
-    <t>9/48</t>
+    <t>ACB109/91</t>
   </si>
   <si>
     <t>NGUYEN MINH NHAT chuyen tien</t>
@@ -737,7 +737,7 @@
     <t>BCNTDMN</t>
   </si>
   <si>
-    <t>9/47</t>
+    <t>ACB109/92</t>
   </si>
   <si>
     <t>NGUYEN VAN XUAN chuyen tien</t>
@@ -749,7 +749,7 @@
     <t>DNVX</t>
   </si>
   <si>
-    <t>9/46</t>
+    <t>ACB109/93</t>
   </si>
   <si>
     <t>Thu phi quan ly tai khoan</t>
@@ -761,7 +761,7 @@
     <t>0414</t>
   </si>
   <si>
-    <t>9/45</t>
+    <t>ACB109/94</t>
   </si>
   <si>
     <t>MAI DUY HOP chuyen tien</t>
@@ -773,13 +773,13 @@
     <t>BCNTDDH</t>
   </si>
   <si>
-    <t>9/44</t>
+    <t>ACB109/95</t>
   </si>
   <si>
     <t>LE VAN TINH CHUYEN KHOAN</t>
   </si>
   <si>
-    <t>9/43</t>
+    <t>ACB109/96</t>
   </si>
   <si>
     <t>LE HUY HOANG chuyen tien</t>
@@ -791,70 +791,70 @@
     <t>BCNTDHH</t>
   </si>
   <si>
-    <t>9/42</t>
-  </si>
-  <si>
-    <t>9/41</t>
+    <t>ACB109/97</t>
+  </si>
+  <si>
+    <t>ACB109/98</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thang toan tien ca MINH CUONG</t>
   </si>
   <si>
-    <t>9/40</t>
+    <t>ACB109/99</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thwnh toan tilafm n cua HOANG TIEN</t>
   </si>
   <si>
-    <t>9/39</t>
+    <t>ACB109/100</t>
   </si>
   <si>
     <t>TT TIEN HAI SAN HD 1419+1354+1359+1369+1378+1389+1402+1408 NGAY 20-09-2026</t>
   </si>
   <si>
-    <t>9/38</t>
+    <t>ACB109/101</t>
   </si>
   <si>
     <t>TT TIEN HAI SAN HD 1351+1360+1370+1379+1390+1400+1411 NGAY 13-09-2026</t>
   </si>
   <si>
-    <t>9/37</t>
+    <t>ACB109/102</t>
   </si>
   <si>
     <t>TT TIEN HAI SAN HD 1412+1350+1361+1371+1380+1391+1401 NGAY 19-09-2026</t>
   </si>
   <si>
-    <t>9/36</t>
-  </si>
-  <si>
-    <t>9/35</t>
-  </si>
-  <si>
-    <t>9/34</t>
+    <t>ACB109/103</t>
+  </si>
+  <si>
+    <t>ACB109/104</t>
+  </si>
+  <si>
+    <t>ACB109/105</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca HOANGVAF</t>
   </si>
   <si>
-    <t>9/33</t>
+    <t>ACB109/106</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau THANH ben da</t>
   </si>
   <si>
-    <t>9/32</t>
-  </si>
-  <si>
-    <t>9/31</t>
-  </si>
-  <si>
-    <t>9/30</t>
+    <t>ACB109/107</t>
+  </si>
+  <si>
+    <t>ACB109/108</t>
+  </si>
+  <si>
+    <t>ACB109/109</t>
   </si>
   <si>
     <t>Phuoc Nguyen TT tien hang HD 1319 den 1373 Cty Cha Va LS</t>
   </si>
   <si>
-    <t>9/29</t>
+    <t>ACB109/110</t>
   </si>
   <si>
     <t>LE MANH THANG chuyen tien.CT tu 0081000209112 LE MANH THANG toi 6000201008933 Cty TNHH Thuy San Cha Va Long Son tai AGRIBANK</t>
@@ -866,7 +866,7 @@
     <t>DLMT</t>
   </si>
   <si>
-    <t>9/28</t>
+    <t>ACB109/111</t>
   </si>
   <si>
     <t>Luong Phu chuyen khoan nhanh qua Zalo</t>
@@ -878,19 +878,19 @@
     <t>BCNTD-LP</t>
   </si>
   <si>
-    <t>9/27</t>
+    <t>ACB109/112</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau Quan Quyen</t>
   </si>
   <si>
-    <t>9/26</t>
+    <t>ACB109/113</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son tam ung mua xang dau</t>
   </si>
   <si>
-    <t>9/25</t>
+    <t>ACB109/114</t>
   </si>
   <si>
     <t>Le thi nhung chuyen khoan nhanh qua Zalo</t>
@@ -902,7 +902,7 @@
     <t>1492-001</t>
   </si>
   <si>
-    <t>9/24</t>
+    <t>ACB109/115</t>
   </si>
   <si>
     <t>LE CONG VUONG chuyen tien</t>
@@ -914,7 +914,7 @@
     <t>DLCV</t>
   </si>
   <si>
-    <t>9/23</t>
+    <t>ACB109/116</t>
   </si>
   <si>
     <t>HUYNH PHUC TOAN chuyen tien</t>
@@ -926,94 +926,94 @@
     <t>DHPT</t>
   </si>
   <si>
-    <t>9/22</t>
+    <t>ACB109/117</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau QUYEN QUAN</t>
   </si>
   <si>
-    <t>9/21</t>
+    <t>ACB109/118</t>
   </si>
   <si>
     <t>TT TIEN HAI SAN HD 1472+1473+1422+1429+1438+1444+1454+1465 NGAY 26-09-2026</t>
   </si>
   <si>
-    <t>9/20</t>
+    <t>ACB109/119</t>
   </si>
   <si>
     <t>TT TIEN HAI SAN HD 1474+1420+1430+1436+1446+1455+1461 NGAY 26-09-2026</t>
   </si>
   <si>
-    <t>9/19</t>
+    <t>ACB109/120</t>
   </si>
   <si>
     <t>TT TIEN HAI SAN HD 1475+1421+1431+1437+1445+1456+1463 NGAY 26-09-2026</t>
   </si>
   <si>
-    <t>9/18</t>
-  </si>
-  <si>
-    <t>9/17</t>
-  </si>
-  <si>
-    <t>9/16</t>
+    <t>ACB109/121</t>
+  </si>
+  <si>
+    <t>ACB109/122</t>
+  </si>
+  <si>
+    <t>ACB109/123</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien cua HOANG</t>
   </si>
   <si>
-    <t>9/15</t>
+    <t>ACB109/124</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca HOANG Ben Da</t>
   </si>
   <si>
-    <t>9/14</t>
-  </si>
-  <si>
-    <t>9/13</t>
-  </si>
-  <si>
-    <t>9/12</t>
+    <t>ACB109/125</t>
+  </si>
+  <si>
+    <t>ACB109/126</t>
+  </si>
+  <si>
+    <t>ACB109/127</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau MINH DUNG</t>
   </si>
   <si>
-    <t>9/11</t>
+    <t>ACB109/128</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau DUC</t>
   </si>
   <si>
-    <t>9/10</t>
+    <t>ACB109/129</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau NAM</t>
   </si>
   <si>
-    <t>9/9</t>
+    <t>ACB109/130</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son dich vu khai bao thue Q3 nam 2026</t>
   </si>
   <si>
-    <t>9/8</t>
-  </si>
-  <si>
-    <t>9/7</t>
+    <t>ACB109/131</t>
+  </si>
+  <si>
+    <t>ACB109/132</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son nop +BHXH+103+00+Q60027I+07709+dong BHXH thang 9 nam 2026+</t>
   </si>
   <si>
-    <t>9/6</t>
+    <t>ACB109/133</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son nop +BHXH+103+00+TA2045A+07709+dong BHXH thang 9 nam 2026+</t>
   </si>
   <si>
-    <t>9/5</t>
+    <t>ACB109/134</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien da cay HONG PHAT 2</t>
@@ -1025,25 +1025,25 @@
     <t>9213</t>
   </si>
   <si>
-    <t>9/4</t>
+    <t>ACB109/135</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca THIEN HUONG</t>
   </si>
   <si>
-    <t>9/3</t>
+    <t>ACB109/136</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau THANH Ben da</t>
   </si>
   <si>
-    <t>9/2</t>
+    <t>ACB109/137</t>
   </si>
   <si>
     <t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca YEN SUONG</t>
   </si>
   <si>
-    <t>9/1</t>
+    <t>ACB109/138</t>
   </si>
   <si>
     <t>Lãi tiền gửi</t>
